--- a/data/trans_orig/P37C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023</t>
+          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4464</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9061</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1716</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10758</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10180</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>9671</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30560</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47743</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>134026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71151</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124599</t>
+          <t>122545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189177</t>
+          <t>192936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245666</t>
+          <t>243930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308502</t>
+          <t>305777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220550</t>
+          <t>219569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259155</t>
+          <t>258176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>483864</t>
+          <t>479540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>552618</t>
+          <t>553196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21027</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75874</t>
+          <t>76592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116640</t>
+          <t>119801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98329</t>
+          <t>98278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132355</t>
+          <t>131546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>203630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276893</t>
+          <t>273081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320856</t>
+          <t>320556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392648</t>
+          <t>393108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450711</t>
+          <t>451111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682325</t>
+          <t>681175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>767593</t>
+          <t>766438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,18%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25870</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49756</t>
+          <t>50359</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133916</t>
+          <t>134840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112276</t>
+          <t>114486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187855</t>
+          <t>187585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239321</t>
+          <t>237082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358522</t>
+          <t>359542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>401844</t>
+          <t>401559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>416522</t>
+          <t>415968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>446379</t>
+          <t>445852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>788170</t>
+          <t>788456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>842519</t>
+          <t>840142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,39 +2904,39 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5322</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,02%</t>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>54478</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61596</t>
+          <t>70085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206948</t>
+          <t>203512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121510</t>
+          <t>122613</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165698</t>
+          <t>168814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>163074</t>
+          <t>173321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>350621</t>
+          <t>351610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>636047</t>
+          <t>637260</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>805998</t>
+          <t>799051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>516504</t>
+          <t>516163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>565380</t>
+          <t>567534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1176924</t>
+          <t>1174755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1397558</t>
+          <t>1384420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>31487</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>95220</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>130395</t>
+          <t>129519</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106400</t>
+          <t>105195</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>133725</t>
+          <t>133376</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>212234</t>
+          <t>208860</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>257780</t>
+          <t>253472</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>386618</t>
+          <t>387446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>424484</t>
+          <t>424872</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>391772</t>
+          <t>392086</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>419991</t>
+          <t>422071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>786181</t>
+          <t>790330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>834537</t>
+          <t>836769</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39981</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63495</t>
+          <t>63089</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>88264</t>
+          <t>88566</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>136690</t>
+          <t>136008</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>83042</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>210495</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>258693</t>
+          <t>256742</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>285514</t>
+          <t>284060</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>438871</t>
+          <t>440476</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>561019</t>
+          <t>562428</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>711955</t>
+          <t>711360</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>868373</t>
+          <t>862031</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -4822,97 +4822,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1181</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>5683</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>4071</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>44976</t>
+          <t>45422</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>72388</t>
+          <t>72958</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>95492</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>123581</t>
+          <t>123811</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>155097</t>
+          <t>154332</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>204706</t>
+          <t>204318</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>227242</t>
+          <t>226867</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>314179</t>
+          <t>313416</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>337644</t>
+          <t>337656</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>525939</t>
+          <t>526650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>558656</t>
+          <t>559418</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>37094</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>104141</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>163464</t>
+          <t>162526</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>73394</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>114404</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>190048</t>
+          <t>189601</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>260180</t>
+          <t>262299</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>569776</t>
+          <t>550491</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>768826</t>
+          <t>771707</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>533214</t>
+          <t>540784</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>722385</t>
+          <t>729519</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1180851</t>
+          <t>1176479</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1467430</t>
+          <t>1470616</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2481958</t>
+          <t>2474193</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2732579</t>
+          <t>2750697</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2792575</t>
+          <t>2786360</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3003513</t>
+          <t>3005311</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5306822</t>
+          <t>5298955</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5646835</t>
+          <t>5645567</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31399</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>42557</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50378</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>101439</t>
+          <t>100121</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>73486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>128217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>62321</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>46017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>82999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>154497</t>
+          <t>162442</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122545</t>
+          <t>131982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192936</t>
+          <t>199303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>277497</t>
+          <t>272391</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243930</t>
+          <t>242546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305777</t>
+          <t>298245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>241369</t>
+          <t>279927</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219569</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258176</t>
+          <t>299660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>518867</t>
+          <t>552319</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479540</t>
+          <t>510316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>553196</t>
+          <t>584521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>711113</t>
+          <t>763886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1520,67 +1520,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9878</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3694</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9729</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>22775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>26712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45983</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96238</t>
+          <t>113480</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76592</t>
+          <t>91548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119801</t>
+          <t>138136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48054</t>
+          <t>72357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98278</t>
+          <t>105513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>173511</t>
+          <t>202589</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131546</t>
+          <t>174708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203630</t>
+          <t>229288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>299585</t>
+          <t>330565</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273081</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320556</t>
+          <t>354734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>416903</t>
+          <t>391699</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393108</t>
+          <t>374618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451111</t>
+          <t>410689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>722264</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681175</t>
+          <t>693117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766438</t>
+          <t>754062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>421990</t>
+          <t>475654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>421990</t>
+          <t>475654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>421990</t>
+          <t>475654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>500229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>932632</t>
+          <t>975883</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>932632</t>
+          <t>975883</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>932632</t>
+          <t>975883</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>758</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>53255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2428,69 +2428,69 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>114244</t>
+          <t>132784</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95382</t>
+          <t>112732</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134840</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>116308</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>100749</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>133078</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>21,42%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>97523</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>84481</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>114486</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>293</t>
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>211766</t>
+          <t>249092</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187585</t>
+          <t>223068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237082</t>
+          <t>276662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>382224</t>
+          <t>436321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359542</t>
+          <t>411514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>401559</t>
+          <t>457629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>432119</t>
+          <t>489616</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>415968</t>
+          <t>471183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>445852</t>
+          <t>505715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>814342</t>
+          <t>925936</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>788456</t>
+          <t>897938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840142</t>
+          <t>957895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533289</t>
+          <t>614925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>541645</t>
+          <t>621310</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>541645</t>
+          <t>621310</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>541645</t>
+          <t>621310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1074934</t>
+          <t>1236235</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1074934</t>
+          <t>1236235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1074934</t>
+          <t>1236235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2884,67 +2884,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5235</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4252</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>22929</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27635</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>45550</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>60511</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>141004</t>
+          <t>158357</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70085</t>
+          <t>137060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203512</t>
+          <t>178650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>146218</t>
+          <t>156277</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122613</t>
+          <t>140514</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168814</t>
+          <t>175755</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>287222</t>
+          <t>314634</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173321</t>
+          <t>286965</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>351610</t>
+          <t>342877</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>712336</t>
+          <t>503981</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>637260</t>
+          <t>482051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>799051</t>
+          <t>526933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>539030</t>
+          <t>548897</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>516163</t>
+          <t>527364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>567534</t>
+          <t>565226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1251366</t>
+          <t>1052878</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1174755</t>
+          <t>1021347</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1384420</t>
+          <t>1081394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>882092</t>
+          <t>694551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>709222</t>
+          <t>733081</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>709222</t>
+          <t>733081</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>709222</t>
+          <t>733081</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1591314</t>
+          <t>1427632</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1591314</t>
+          <t>1427632</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1591314</t>
+          <t>1427632</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29198</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39645</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>21402</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>41770</t>
+          <t>48974</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>37354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>64119</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>112730</t>
+          <t>127939</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95220</t>
+          <t>110731</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>129519</t>
+          <t>147015</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>119640</t>
+          <t>132018</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>105195</t>
+          <t>117265</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>133376</t>
+          <t>146903</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>232370</t>
+          <t>259957</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208860</t>
+          <t>236686</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>253472</t>
+          <t>286804</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>405974</t>
+          <t>432794</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>387446</t>
+          <t>409702</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>424872</t>
+          <t>451207</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>407123</t>
+          <t>454170</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>392086</t>
+          <t>437416</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>422071</t>
+          <t>469453</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>813097</t>
+          <t>886964</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>790330</t>
+          <t>859417</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>836769</t>
+          <t>912835</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>553669</t>
+          <t>601541</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>553669</t>
+          <t>601541</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>553669</t>
+          <t>601541</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>544421</t>
+          <t>606903</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>544421</t>
+          <t>606903</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>544421</t>
+          <t>606903</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1098090</t>
+          <t>1208444</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1098090</t>
+          <t>1208444</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1098090</t>
+          <t>1208444</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,67 +4170,67 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>6037</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4248,22 +4248,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63089</t>
+          <t>71271</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>88566</t>
+          <t>99918</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>86275</t>
+          <t>93927</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>136008</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>161515</t>
+          <t>178884</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>85587</t>
+          <t>160844</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>210495</t>
+          <t>198097</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>272424</t>
+          <t>299632</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>256742</t>
+          <t>282980</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>284060</t>
+          <t>313537</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>499082</t>
+          <t>322594</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>440476</t>
+          <t>309786</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>562428</t>
+          <t>335296</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>771506</t>
+          <t>622225</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>711360</t>
+          <t>601337</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>862031</t>
+          <t>641629</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>365763</t>
+          <t>403932</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>365763</t>
+          <t>403932</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>365763</t>
+          <t>403932</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>602989</t>
+          <t>435499</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>602989</t>
+          <t>435499</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>602989</t>
+          <t>435499</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>968752</t>
+          <t>839430</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>968752</t>
+          <t>839430</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>968752</t>
+          <t>839430</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>62681</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>51188</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>66708</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>91503</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>72958</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>95492</t>
+          <t>103868</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>139141</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>123811</t>
+          <t>137881</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>154332</t>
+          <t>172330</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>216164</t>
+          <t>234232</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>204318</t>
+          <t>222410</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>226867</t>
+          <t>246896</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>326159</t>
+          <t>356475</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>313416</t>
+          <t>343323</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>337656</t>
+          <t>369258</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>542323</t>
+          <t>590707</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>526650</t>
+          <t>572286</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>559418</t>
+          <t>608619</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>279862</t>
+          <t>306689</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>279862</t>
+          <t>306689</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279862</t>
+          <t>306689</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>422849</t>
+          <t>461315</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>422849</t>
+          <t>461315</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>422849</t>
+          <t>461315</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>702711</t>
+          <t>768004</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>702711</t>
+          <t>768004</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>702711</t>
+          <t>768004</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,17 +5569,17 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>56548</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>133877</t>
+          <t>166341</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>141103</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>162526</t>
+          <t>201062</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>115476</t>
+          <t>128026</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>189601</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>262299</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>696038</t>
+          <t>780317</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>550491</t>
+          <t>724238</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>771707</t>
+          <t>836341</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>663984</t>
+          <t>741464</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>540784</t>
+          <t>698674</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>729519</t>
+          <t>783147</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1360022</t>
+          <t>1521781</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1176479</t>
+          <t>1453889</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1470616</t>
+          <t>1590458</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2566204</t>
+          <t>2509916</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2474193</t>
+          <t>2449736</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2750697</t>
+          <t>2571303</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2861786</t>
+          <t>2843378</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2786360</t>
+          <t>2799457</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3005311</t>
+          <t>2889756</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5427989</t>
+          <t>5353294</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5298955</t>
+          <t>5281697</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5645567</t>
+          <t>5424714</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
